--- a/converted_files/835/835-provider-level-adjustment.xlsx
+++ b/converted_files/835/835-provider-level-adjustment.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cbecb80b363c8541f873</t>
+          <t>6a04cc5a1ef26d534baf14fb</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/835/835-provider-level-adjustment.xlsx
+++ b/converted_files/835/835-provider-level-adjustment.xlsx
@@ -1107,7 +1107,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf14fb</t>
+          <t>6a32cb6297613a0e4990693b</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">

--- a/converted_files/835/835-provider-level-adjustment.xlsx
+++ b/converted_files/835/835-provider-level-adjustment.xlsx
@@ -6,7 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Payments and Service Lines" r:id="rId3" sheetId="1"/>
+    <sheet name="Transactions" r:id="rId3" sheetId="1"/>
+    <sheet name="ProviderAdjustments" r:id="rId4" sheetId="2"/>
+    <sheet name="Service Lines" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -59,6 +61,1811 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AX4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9185e</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H2"/>
+      <c r="I2" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>TRN1</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
+      <c r="Q2"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="U2"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER1_NPI</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
+      <c r="AN2"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9187e</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVER_ACCT_1</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>45651.0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>CHECK_1</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
+      <c r="Q3"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="U3"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER2_NPI</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
+      <c r="AN3"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede918a5</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0003</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H4"/>
+      <c r="I4" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TRN3</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>ANY PLAN USA</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1 WALK THIS WAY</t>
+        </is>
+      </c>
+      <c r="Q4"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>ANYCITY</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>45209</t>
+        </is>
+      </c>
+      <c r="U4"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>8661112222</t>
+        </is>
+      </c>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>8002223333</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>EDI.SUPPORT@ANYPAYER.COM</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ADDNL_PAYER_ID</t>
+        </is>
+      </c>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER3_NPI</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2255 ANY ROAD</t>
+        </is>
+      </c>
+      <c r="AN4"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>ANY CITY</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>12211</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_IDENTIFICATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID3</t>
+        </is>
+      </c>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:BC7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionType</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>FileName</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TransactionControlNumber</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TotalPaymentAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>CreditOrDebitFlagCode</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentMethodType</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ReceiverAccountNumber</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>PaymentDate</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>CheckOrEftTraceNumber</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>PayerEin</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>ProductionDate</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentificationType</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>PayerIdentifier</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>PayerName</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressLine2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressCity</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressStateCode</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAddressZipCode</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1Name</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact1ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2Name</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Type</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber1Number</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Type</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>PayerContact2ContactNumber2Number</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>PayerAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentificationType</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeIdentifier</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeLastNameOrOrgName</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressLine2</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressCity</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressStateCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAddressZipCode</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Type</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId1Identification</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Type</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>PayeeAdditionalId2Identification</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodName</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderIdentifier</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>FiscalPeriodDate</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReason</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentReferenceIdentification</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>ProviderAdjustmentAmount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9185e</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H2"/>
+      <c r="I2" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>TRN1</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
+      <c r="AZ2" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="BA2" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="BB2" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC2" s="1" t="n">
+        <v>298.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9185e</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H3"/>
+      <c r="I3" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TRN1</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID1</t>
+        </is>
+      </c>
+      <c r="AZ3" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="BA3" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>-298.18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9185e</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H4"/>
+      <c r="I4" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TRN1</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID99</t>
+        </is>
+      </c>
+      <c r="AZ4" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="BA4" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>298.18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9185e</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H5"/>
+      <c r="I5" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TRN1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID99</t>
+        </is>
+      </c>
+      <c r="AZ5" s="4" t="n">
+        <v>45657.0</v>
+      </c>
+      <c r="BA5" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>-298.18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede9187e</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>500.0</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVER_ACCT_1</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>45651.0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>CHECK_1</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID2</t>
+        </is>
+      </c>
+      <c r="AZ6" s="4" t="n">
+        <v>45291.0</v>
+      </c>
+      <c r="BA6" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC6" s="1" t="n">
+        <v>298.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>6a68fd29aa71f5c1ede918a5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>835-provider-level-adjustment.dat</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>0003</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>NON_PAYMENT</t>
+        </is>
+      </c>
+      <c r="H7"/>
+      <c r="I7" s="4" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TRN3</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PAYER_ID_1</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>45649.0</v>
+      </c>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>PAYEE_ID3</t>
+        </is>
+      </c>
+      <c r="AZ7" s="4" t="n">
+        <v>44926.0</v>
+      </c>
+      <c r="BA7" s="3" t="inlineStr">
+        <is>
+          <t>WO</t>
+        </is>
+      </c>
+      <c r="BB7" s="3" t="inlineStr">
+        <is>
+          <t>3243079284</t>
+        </is>
+      </c>
+      <c r="BC7" s="1" t="n">
+        <v>298.18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:GZ2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -410,37 +2217,37 @@
       </c>
       <c r="BR1" s="3" t="inlineStr">
         <is>
+          <t>PayeeTaxId</t>
+        </is>
+      </c>
+      <c r="BS1" s="3" t="inlineStr">
+        <is>
           <t>PayeeLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="BS1" s="3" t="inlineStr">
+      <c r="BT1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine</t>
         </is>
       </c>
-      <c r="BT1" s="3" t="inlineStr">
+      <c r="BU1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressLine2</t>
         </is>
       </c>
-      <c r="BU1" s="3" t="inlineStr">
+      <c r="BV1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressCity</t>
         </is>
       </c>
-      <c r="BV1" s="3" t="inlineStr">
+      <c r="BW1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressStateCode</t>
         </is>
       </c>
-      <c r="BW1" s="3" t="inlineStr">
+      <c r="BX1" s="3" t="inlineStr">
         <is>
           <t>PayeeAddressZipCode</t>
-        </is>
-      </c>
-      <c r="BX1" s="3" t="inlineStr">
-        <is>
-          <t>PayeeContacts</t>
         </is>
       </c>
       <c r="BY1" s="3" t="inlineStr">
@@ -1107,7 +2914,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6297613a0e4990693b</t>
+          <t>6a68fd29aa71f5c1ede918c7</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1195,7 +3002,7 @@
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>PAYER_ID</t>
+          <t>PAYER_ID_1</t>
         </is>
       </c>
       <c r="X2" s="4" t="n">
@@ -1322,31 +3129,35 @@
       </c>
       <c r="BR2" s="3" t="inlineStr">
         <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="BS2" s="3" t="inlineStr">
+        <is>
           <t>PROVIDER</t>
         </is>
       </c>
-      <c r="BS2" s="3" t="inlineStr">
+      <c r="BT2" s="3" t="inlineStr">
         <is>
           <t>2255 ANY ROAD</t>
         </is>
       </c>
-      <c r="BT2"/>
-      <c r="BU2" s="3" t="inlineStr">
+      <c r="BU2"/>
+      <c r="BV2" s="3" t="inlineStr">
         <is>
           <t>ANY CITY</t>
         </is>
       </c>
-      <c r="BV2" s="3" t="inlineStr">
+      <c r="BW2" s="3" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="BW2" s="3" t="inlineStr">
+      <c r="BX2" s="3" t="inlineStr">
         <is>
           <t>12211</t>
         </is>
       </c>
-      <c r="BX2"/>
       <c r="BY2" s="3" t="inlineStr">
         <is>
           <t>PAYEE_IDENTIFICATION_NUMBER</t>
